--- a/data/trans_bre/IP04D$individual-Edad-trans_bre.xlsx
+++ b/data/trans_bre/IP04D$individual-Edad-trans_bre.xlsx
@@ -632,32 +632,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-19,38; -1,7</t>
+          <t>-19,77; -1,89</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-12,24; 5,16</t>
+          <t>-12,48; 5,41</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-19,42; 3,05</t>
+          <t>-18,89; 3,86</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-44,54; -4,16</t>
+          <t>-45,76; -5,84</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-36,9; 20,71</t>
+          <t>-36,8; 21,38</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-63,26; 19,99</t>
+          <t>-61,04; 22,08</t>
         </is>
       </c>
     </row>
@@ -712,32 +712,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-7,2; 6,56</t>
+          <t>-6,38; 6,86</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1,62; 14,6</t>
+          <t>1,65; 15,98</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-6,97; 6,9</t>
+          <t>-7,05; 7,12</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-23,09; 26,92</t>
+          <t>-21,14; 28,21</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>4,93; 55,78</t>
+          <t>5,0; 61,89</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-34,88; 51,49</t>
+          <t>-34,3; 52,13</t>
         </is>
       </c>
     </row>
@@ -792,32 +792,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-11,38; 5,51</t>
+          <t>-11,68; 6,85</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-7,2; 7,97</t>
+          <t>-7,59; 7,6</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-12,91; 1,74</t>
+          <t>-13,41; 0,93</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-29,61; 19,01</t>
+          <t>-30,21; 23,47</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-21,91; 31,02</t>
+          <t>-22,55; 29,15</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-52,29; 12,58</t>
+          <t>-54,01; 7,67</t>
         </is>
       </c>
     </row>
@@ -872,32 +872,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-12,25; 4,77</t>
+          <t>-12,37; 4,01</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-3,36; 13,89</t>
+          <t>-3,48; 12,91</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-16,17; 2,25</t>
+          <t>-16,05; 1,9</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-36,19; 18,35</t>
+          <t>-36,22; 15,04</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-10,87; 59,43</t>
+          <t>-11,79; 54,59</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-55,31; 12,82</t>
+          <t>-56,17; 12,2</t>
         </is>
       </c>
     </row>
@@ -952,32 +952,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-7,06; 0,53</t>
+          <t>-7,22; 0,51</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-1,04; 6,94</t>
+          <t>-0,53; 7,31</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-9,38; -0,92</t>
+          <t>-9,54; -0,54</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-21,49; 1,52</t>
+          <t>-21,44; 1,72</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-3,73; 25,45</t>
+          <t>-1,79; 27,57</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-39,39; -4,53</t>
+          <t>-40,27; -2,88</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP04D$individual-Edad-trans_bre.xlsx
+++ b/data/trans_bre/IP04D$individual-Edad-trans_bre.xlsx
@@ -632,32 +632,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-19,77; -1,89</t>
+          <t>-19,4; -1,55</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-12,48; 5,41</t>
+          <t>-12,52; 4,56</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-18,89; 3,86</t>
+          <t>-17,7; 4,73</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-45,76; -5,84</t>
+          <t>-44,53; -4,19</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-36,8; 21,38</t>
+          <t>-37,09; 21,38</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-61,04; 22,08</t>
+          <t>-61,62; 28,81</t>
         </is>
       </c>
     </row>
@@ -712,32 +712,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-6,38; 6,86</t>
+          <t>-6,55; 6,88</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1,65; 15,98</t>
+          <t>1,05; 15,79</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-7,05; 7,12</t>
+          <t>-7,33; 7,26</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-21,14; 28,21</t>
+          <t>-21,69; 28,49</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>5,0; 61,89</t>
+          <t>3,74; 61,67</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-34,3; 52,13</t>
+          <t>-36,12; 53,95</t>
         </is>
       </c>
     </row>
@@ -792,32 +792,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-11,68; 6,85</t>
+          <t>-11,77; 5,68</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-7,59; 7,6</t>
+          <t>-7,61; 8,2</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-13,41; 0,93</t>
+          <t>-13,1; 1,18</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-30,21; 23,47</t>
+          <t>-30,18; 18,76</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-22,55; 29,15</t>
+          <t>-22,72; 32,42</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-54,01; 7,67</t>
+          <t>-53,47; 9,36</t>
         </is>
       </c>
     </row>
@@ -872,32 +872,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-12,37; 4,01</t>
+          <t>-11,5; 4,74</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-3,48; 12,91</t>
+          <t>-2,9; 12,73</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-16,05; 1,9</t>
+          <t>-16,73; 2,1</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-36,22; 15,04</t>
+          <t>-32,79; 17,93</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-11,79; 54,59</t>
+          <t>-9,84; 54,25</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-56,17; 12,2</t>
+          <t>-55,42; 12,58</t>
         </is>
       </c>
     </row>
@@ -952,32 +952,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-7,22; 0,51</t>
+          <t>-7,34; 0,97</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-0,53; 7,31</t>
+          <t>-0,98; 6,79</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-9,54; -0,54</t>
+          <t>-9,07; 0,12</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-21,44; 1,72</t>
+          <t>-21,84; 3,23</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-1,79; 27,57</t>
+          <t>-3,48; 25,5</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-40,27; -2,88</t>
+          <t>-38,81; 0,71</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP04D$individual-Edad-trans_bre.xlsx
+++ b/data/trans_bre/IP04D$individual-Edad-trans_bre.xlsx
@@ -518,8 +518,10 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="n">
-        <v/>
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Población que dispone de calefacción individual en su vivienda</t>
+        </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
@@ -604,7 +606,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>-7,84</t>
+          <t>-6,0</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -619,7 +621,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>-31,64%</t>
+          <t>-26,06%</t>
         </is>
       </c>
     </row>
@@ -632,32 +634,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-19,4; -1,55</t>
+          <t>-19,38; -1,7</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-12,52; 4,56</t>
+          <t>-12,24; 5,16</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-17,7; 4,73</t>
+          <t>-17,43; 4,15</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-44,53; -4,19</t>
+          <t>-44,54; -4,16</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-37,09; 21,38</t>
+          <t>-36,9; 20,71</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-61,62; 28,81</t>
+          <t>-61,09; 25,39</t>
         </is>
       </c>
     </row>
@@ -684,7 +686,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>-0,02</t>
+          <t>-0,54</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -699,7 +701,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>-0,14%</t>
+          <t>-3,04%</t>
         </is>
       </c>
     </row>
@@ -712,32 +714,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-6,55; 6,88</t>
+          <t>-7,2; 6,56</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1,05; 15,79</t>
+          <t>1,62; 14,6</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-7,33; 7,26</t>
+          <t>-7,66; 6,51</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-21,69; 28,49</t>
+          <t>-23,09; 26,92</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>3,74; 61,67</t>
+          <t>4,93; 55,78</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-36,12; 53,95</t>
+          <t>-36,36; 50,58</t>
         </is>
       </c>
     </row>
@@ -764,7 +766,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>-5,89</t>
+          <t>-5,49</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -779,7 +781,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>-28,57%</t>
+          <t>-26,85%</t>
         </is>
       </c>
     </row>
@@ -792,32 +794,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-11,77; 5,68</t>
+          <t>-11,38; 5,51</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-7,61; 8,2</t>
+          <t>-7,2; 7,97</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-13,1; 1,18</t>
+          <t>-12,55; 2,13</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-30,18; 18,76</t>
+          <t>-29,61; 19,01</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-22,72; 32,42</t>
+          <t>-21,91; 31,02</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-53,47; 9,36</t>
+          <t>-51,89; 14,95</t>
         </is>
       </c>
     </row>
@@ -844,7 +846,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>-5,38</t>
+          <t>-3,5</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -859,7 +861,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>-24,67%</t>
+          <t>-16,01%</t>
         </is>
       </c>
     </row>
@@ -872,32 +874,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-11,5; 4,74</t>
+          <t>-12,25; 4,77</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-2,9; 12,73</t>
+          <t>-3,36; 13,89</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-16,73; 2,1</t>
+          <t>-12,86; 3,69</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-32,79; 17,93</t>
+          <t>-36,19; 18,35</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-9,84; 54,25</t>
+          <t>-10,87; 59,43</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-55,42; 12,58</t>
+          <t>-45,5; 21,51</t>
         </is>
       </c>
     </row>
@@ -924,7 +926,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>-4,41</t>
+          <t>-3,58</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -939,7 +941,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>-21,44%</t>
+          <t>-17,41%</t>
         </is>
       </c>
     </row>
@@ -952,32 +954,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-7,34; 0,97</t>
+          <t>-7,06; 0,53</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-0,98; 6,79</t>
+          <t>-1,04; 6,94</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-9,07; 0,12</t>
+          <t>-8,0; 0,22</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-21,84; 3,23</t>
+          <t>-21,49; 1,52</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-3,48; 25,5</t>
+          <t>-3,73; 25,45</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-38,81; 0,71</t>
+          <t>-34,2; 1,44</t>
         </is>
       </c>
     </row>
